--- a/www/download/IND.empe.s.un.rpO1.xlsx
+++ b/www/download/IND.empe.s.un.rpO1.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7.001</t>
+          <t>7000815</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.121</t>
+          <t>7120800</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>7199035</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.404</t>
+          <t>7404275</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.566</t>
+          <t>7565955</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.737</t>
+          <t>7736810.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.864</t>
+          <t>7864119.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.082</t>
+          <t>8082269.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>8251604.61</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>8480132.7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8.741</t>
+          <t>8740938.13122661</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8.965</t>
+          <t>8964969.8520771</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>9.202</t>
+          <t>9202230.54737272</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9.942</t>
+          <t>9942083.06364353</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10.452</t>
+          <t>10451797.5846695</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.126</t>
+          <t>3126174</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>3122592</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3150546</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.184</t>
+          <t>3184499</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>3238962</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>3277641</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3300196</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>3292549</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.302</t>
+          <t>3301853</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.315</t>
+          <t>3314964</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>3352668</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>3407542</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3479521</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.569</t>
+          <t>3569279</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>3543030</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>3168922</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>3173179</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>3198472</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>3267797</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>3322574</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3407095</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3469614</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3469893</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>3471630</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>3507058</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>3563414</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>3609450</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>3672415</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>3738337</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3716888</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>2713209.70272858</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2733215.13993289</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2590119.06683022</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.528</t>
+          <t>2528268.60645396</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2390124.26970069</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>2325500</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>2272300</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2280600</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>2365200</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.432</t>
+          <t>2432000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2522700</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>2631000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2740300</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>2817200</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>2723500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>59.052</t>
+          <t>59051895.1142841</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.777</t>
+          <t>57777028.9872046</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.432</t>
+          <t>58431793.2642276</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.853</t>
+          <t>57853251.1750386</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.702</t>
+          <t>60701750.7065571</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>62.692</t>
+          <t>62691673.2272644</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63.064</t>
+          <t>63064441.1552358</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.474</t>
+          <t>65474125.4640584</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>66.734</t>
+          <t>66733664.4534825</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>70.286</t>
+          <t>70285959.9653567</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>72.221</t>
+          <t>72221491.2069989</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>73.868</t>
+          <t>73868122.3176669</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>74.771</t>
+          <t>74770957.8028244</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>75.799</t>
+          <t>75799138.0041801</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>76.071</t>
+          <t>76070715.5490115</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12.163</t>
+          <t>12163122.9926407</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.209</t>
+          <t>12208770.2160367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.429</t>
+          <t>12428724.99891</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>12680214.99891</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>13075604.99891</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>13480109.99891</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.708</t>
+          <t>13707879.99891</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.048</t>
+          <t>14047644.99891</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14.355</t>
+          <t>14354944.99891</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14.633</t>
+          <t>14633084.99891</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14.847</t>
+          <t>14846974.99891</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15.135</t>
+          <t>15135234.99891</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>15.444</t>
+          <t>15443969.99891</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>15.745</t>
+          <t>15744979.99891</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>15432784.99891</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>230.89</t>
+          <t>230890099.057785</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>239.098</t>
+          <t>239097902.1753</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>247.449</t>
+          <t>247449075.19598</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>255.805</t>
+          <t>255804836.74459</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>264.115</t>
+          <t>264114959.887512</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>272.359</t>
+          <t>272358762.348075</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>281.876</t>
+          <t>281876488.827175</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>290.801</t>
+          <t>290801070.04668</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>299.812</t>
+          <t>299812086.919296</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>309.298</t>
+          <t>309297608.0464</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>318.359</t>
+          <t>318358845.45495</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>327.313</t>
+          <t>327312872.742</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>336.439</t>
+          <t>336438611.08569</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>345.235</t>
+          <t>345235373.61768</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>354.245</t>
+          <t>354245480.51664</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223716.495232719</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225937.149256762</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228763.11685584</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233286.523036485</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237983.052303308</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241700</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262900</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273900</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>285800</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296100</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>308800</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326600</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>325400</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.436</t>
+          <t>4435553</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>4446554</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.419</t>
+          <t>4418903</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>4300841</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>4102608</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t>4083040</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.099</t>
+          <t>4099050</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>4085348</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>3981167</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.011</t>
+          <t>4011059</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>4084331</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>4160620</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>4279460</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>4335790</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.254</t>
+          <t>4253931</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>33.852</t>
+          <t>33852000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33.756</t>
+          <t>33756000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.647</t>
+          <t>33647000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.046</t>
+          <t>34046000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.567</t>
+          <t>34567000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.229</t>
+          <t>35229000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.333</t>
+          <t>35333000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>35093000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>34.653</t>
+          <t>34653000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>34.658</t>
+          <t>34658000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>34480000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34.684</t>
+          <t>34684000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.288</t>
+          <t>35288000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.843</t>
+          <t>35843000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.862</t>
+          <t>35861788.1040119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>2352191</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.386</t>
+          <t>2385719</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>2433941</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>2477644</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2503931</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>2527201</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.561</t>
+          <t>2560629</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2559618</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2530109</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>2523517</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.554</t>
+          <t>2553816</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2610456</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>2687817</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2732763.79562092</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.651</t>
+          <t>2650577.70651737</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11.022</t>
+          <t>11021902</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.232</t>
+          <t>11231600</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.825</t>
+          <t>11825100</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12409600</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>13075603</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13.815</t>
+          <t>13814700</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.285</t>
+          <t>14284700</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.666</t>
+          <t>14666200</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15.204</t>
+          <t>15203700</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>15.763</t>
+          <t>15762800</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16.458</t>
+          <t>16458000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17180200</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>17.759</t>
+          <t>17758900</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>17.695</t>
+          <t>17694600</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>16.561</t>
+          <t>16561500</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>589900</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>573000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>568500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>554400</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529700</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>520800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529799.999845246</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538300.000508112</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>541700</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>537899.999595459</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558600</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>594899.999484977</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>597100.00008625</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606000</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>546930.555416823</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>1771700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1799200</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>1865400</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1920200</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>1968200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>2013300</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>2050900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>2076500</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2080100</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>2088500</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2118800</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>2153300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>2201400</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.234</t>
+          <t>2234100</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2156900</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20.264</t>
+          <t>20263700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.419</t>
+          <t>20419300</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20.574</t>
+          <t>20574300</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20.968</t>
+          <t>20967600</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21.455</t>
+          <t>21455400</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22.102</t>
+          <t>22102200</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>22559900</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.725</t>
+          <t>22724800</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22.759</t>
+          <t>22759200</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22.768</t>
+          <t>22768400</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.875</t>
+          <t>22874800</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>23.097</t>
+          <t>23096800</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>23.444</t>
+          <t>23444000</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23580100</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>23.244</t>
+          <t>23244398.5763359</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>23.964</t>
+          <t>23964000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24.245</t>
+          <t>24245000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24790000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.156</t>
+          <t>25156000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>25.577</t>
+          <t>25577000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26.013</t>
+          <t>26013000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>26.297</t>
+          <t>26297000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26.409</t>
+          <t>26409000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26.475</t>
+          <t>26475000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26.731</t>
+          <t>26731000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>27.093</t>
+          <t>27093000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27310000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>27.438</t>
+          <t>27438000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>27.505</t>
+          <t>27505000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>26.766</t>
+          <t>26766000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.406</t>
+          <t>2406295</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.405</t>
+          <t>2405289</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>2403379</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2517762</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>2573625</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.595</t>
+          <t>2595099</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>2643861</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>2744046</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>2797251</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.903</t>
+          <t>2902927</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>2918404</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>3031348</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3110083</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3119816</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>3091013</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>3333796</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>3298792</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3304041</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.402</t>
+          <t>3401781</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.478</t>
+          <t>3478082</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.562</t>
+          <t>3562351</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>3589329</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>3598020</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>3647173</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.599</t>
+          <t>3599362</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>3627317</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.674</t>
+          <t>3673501</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>3682953</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>3646566</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.561</t>
+          <t>3560689</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>29.411</t>
+          <t>29411065.6105816</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.648</t>
+          <t>30648326.955304</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.685</t>
+          <t>32685452.8836112</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31.287</t>
+          <t>31286762.9587007</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>33.271</t>
+          <t>33270823.1410138</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>32.856</t>
+          <t>32855950.6864638</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35.315</t>
+          <t>35315212.263243</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>35.183</t>
+          <t>35183073.6895503</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>33.625</t>
+          <t>33625209.8336917</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>34.679</t>
+          <t>34679252.9202777</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>36.447</t>
+          <t>36447413.5998256</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>38.129</t>
+          <t>38129208.872769</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>40.067</t>
+          <t>40066868.4692204</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>40.926</t>
+          <t>40926077.3173692</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>42.189</t>
+          <t>42188967.0098096</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>176.495</t>
+          <t>176494761.786607</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>182.775</t>
+          <t>182774529.04854</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>185.732</t>
+          <t>185731925.86811</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>188.117</t>
+          <t>188117176.817533</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>187.86</t>
+          <t>187860282.911458</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>194.375</t>
+          <t>194375133.794676</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>198.162</t>
+          <t>198161729.547954</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>192.288</t>
+          <t>192288381.001002</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>198.163</t>
+          <t>198163090.308057</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>198.994</t>
+          <t>198994015.455626</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>199.767</t>
+          <t>199766774.117651</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>197.538</t>
+          <t>197538291.383765</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>191.106</t>
+          <t>191105556.791384</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>193.616</t>
+          <t>193615701.074433</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>195.621</t>
+          <t>195621012.204717</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1017604.10366158</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1063276.0353731</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>1122101.73114926</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1223841</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1310600.97593877</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1381335.80857661</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1431707</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1461166</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1494199.83863608</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.541</t>
+          <t>1541199</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1629775</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1713951</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1761877</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1729924</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1584972</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15.959</t>
+          <t>15958500</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16.051</t>
+          <t>16051300</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16.135</t>
+          <t>16135000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16.306</t>
+          <t>16306300</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.559</t>
+          <t>16559000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16.883</t>
+          <t>16882900</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17.315</t>
+          <t>17314800</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17.717</t>
+          <t>17717200</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17.972</t>
+          <t>17971600</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18.029</t>
+          <t>18029200</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18.359</t>
+          <t>18359400</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18.796</t>
+          <t>18796200</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19120100</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19290100</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>19033300</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>53.767</t>
+          <t>53766608.2829578</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.252</t>
+          <t>54251580.7304874</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>54.767</t>
+          <t>54766801.4608104</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54.304</t>
+          <t>54303584.0121397</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53.699</t>
+          <t>53698651.5500802</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>53.778</t>
+          <t>53778208.9583263</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53800176.4988066</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53.22</t>
+          <t>53220101.5929844</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53.165</t>
+          <t>53164769.1708257</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53.333</t>
+          <t>53333460.660155</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>53.676</t>
+          <t>53676055.1024794</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>54.501</t>
+          <t>54500985.1639254</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>54.736</t>
+          <t>54736152.7603184</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>53.523</t>
+          <t>53522793.7423068</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>49.344</t>
+          <t>49343702.106554</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12.899</t>
+          <t>12899000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13200000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13.405</t>
+          <t>13405000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12.296</t>
+          <t>12296000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12.663</t>
+          <t>12663000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13.361</t>
+          <t>13361000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13.659</t>
+          <t>13659000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14.182</t>
+          <t>14182000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14.403</t>
+          <t>14403000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14.894</t>
+          <t>14894000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>15186000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>15.551</t>
+          <t>15551000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15970000</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16.067</t>
+          <t>16067444.5297832</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16.019</t>
+          <t>16019062.9800307</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1202600</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1149300</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1148200</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1186500</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1164900</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1123800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1078500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>1112900</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1133100</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1158800</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1210700</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1252100</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1319100</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343800</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1243497.35069574</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197867.906976744</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>203369.76744186</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209373.023255814</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219278.604651163</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231283.255813953</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244389.302325581</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>258796.744186047</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267800</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272900</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279300</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>288200</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299200</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>313300</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>328800</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>331900</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825532.764700584</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>812147.350767697</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>799977.275106245</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>819181.568266706</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814677.128248328</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>799300</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808025.625</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>841925.625</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875367.654028436</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>909412.203791469</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>951100</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>994800</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1011401.69491525</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>865500</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20.399</t>
+          <t>20399107.2116234</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21.259</t>
+          <t>21258890.5286284</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22450245.9910663</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23.215</t>
+          <t>23214967.9702403</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24.044</t>
+          <t>24043575.9968171</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>24.921</t>
+          <t>24921294.4908936</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25.354</t>
+          <t>25353729.0216609</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25.781</t>
+          <t>25781358.3755998</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>26.229</t>
+          <t>26228592.2350558</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27179620.783703</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>27.858</t>
+          <t>27857608.0844511</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>28.869</t>
+          <t>28869197.0308023</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29449905.6809756</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>31.816</t>
+          <t>31815688.6884885</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>31.359</t>
+          <t>31358912.4825643</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122463.736798588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123005.017926314</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123495.302319692</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125209.060997641</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126902.689385716</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128335.071345203</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131772.967257186</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134354.368171712</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133263.808734455</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131304.73504799</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133117.864507571</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135939.780428245</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140257.853856829</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143503.761848436</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144492.532243455</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.014</t>
+          <t>6014055</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6150384</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.354</t>
+          <t>6354323</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6.565</t>
+          <t>6565022</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6810114</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6.988</t>
+          <t>6988176</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.152</t>
+          <t>7151976</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>7198960</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7.167</t>
+          <t>7167465</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>7.083</t>
+          <t>7083353</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7.105</t>
+          <t>7105241</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.227</t>
+          <t>7227305</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>7.425</t>
+          <t>7424695</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7550421</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>7.473</t>
+          <t>7472568</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8.714</t>
+          <t>8713700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.725</t>
+          <t>8724700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.863</t>
+          <t>8863200</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8.938</t>
+          <t>8938400</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>8896000</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.354</t>
+          <t>9354100</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.207</t>
+          <t>10206600</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9879500</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.891</t>
+          <t>9890800</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10.084</t>
+          <t>10083800</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10.436</t>
+          <t>10436300</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>10.963</t>
+          <t>10962900</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>11604900</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12.126</t>
+          <t>12125800</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>12.207</t>
+          <t>12206700</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.576</t>
+          <t>3575800</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.618</t>
+          <t>3617900</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>3723500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>3841400</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.923</t>
+          <t>3923400</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>4002100</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4060400</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>4120686.93652677</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>4086993.59017837</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4.117</t>
+          <t>4116888.09375398</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>4128100</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>4356800</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>4.375</t>
+          <t>4374885.41420007</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>4.396</t>
+          <t>4395773.57136985</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4.314</t>
+          <t>4314259.55116487</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>5814106.78915309</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5.894</t>
+          <t>5894010.69882498</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>5399182.80766852</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5.182</t>
+          <t>5181699.07235622</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5.971</t>
+          <t>5971000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>5881500</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.787</t>
+          <t>5786700</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>6137700</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5900300</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6.407</t>
+          <t>6407500</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>6162200</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>6411600</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>6436500</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6.513</t>
+          <t>6513000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>6.583</t>
+          <t>6583087.35589215</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>64.261</t>
+          <t>64260852.7275049</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>62.37</t>
+          <t>62370125.243572</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62.201</t>
+          <t>62200950.4041932</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>59.854</t>
+          <t>59853721.200772</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>60.787</t>
+          <t>60787342.1386412</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>61.691</t>
+          <t>61691101.5357199</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>62.298</t>
+          <t>62297793.6298094</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>62.039</t>
+          <t>62039441.3470101</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>62.159</t>
+          <t>62159453.1953076</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>62.522</t>
+          <t>62522331.8698624</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>63.551</t>
+          <t>63551338.8363913</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>63.928</t>
+          <t>63927636.7601688</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>64.757</t>
+          <t>64757004.4029572</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>64.97</t>
+          <t>64970283.6939326</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>62.523</t>
+          <t>62523399.1033319</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>1968591</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.011</t>
+          <t>2010790</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>1991030</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>1968805</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1900130</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1856325</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>1858161</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1854155</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>1852106</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1803218</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1818745</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1856518</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>1890537</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>1933007</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.848</t>
+          <t>1848236</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>741551</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>730953</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713568</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713561</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>723519</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>738444</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>745890</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>755607</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756323</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>759283</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760350</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772331</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>797110</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>820699</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>800526</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>3847799.99999621</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>3819099.99999627</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>3768000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3836300</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>3917600.00000346</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>4022900</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>4123600</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>4134200.00000303</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>4127600</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>4091200</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>4103200</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4170400</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>4267900</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>4320700</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>4228338.56512301</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10.192</t>
+          <t>10191553.5137728</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.493</t>
+          <t>10492770.9441879</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10.497</t>
+          <t>10497406.3031203</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.782</t>
+          <t>10781896.2598939</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10.736</t>
+          <t>10736172.6216076</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>11.362</t>
+          <t>11362161.4429044</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11.051</t>
+          <t>11051450.6784838</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>11470065.2458555</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11.529</t>
+          <t>11529302.2804298</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>11.812</t>
+          <t>11811661.4028832</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12.473</t>
+          <t>12473341.4731386</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12.479</t>
+          <t>12479040.6647304</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>12.535</t>
+          <t>12535197.1165437</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>12.937</t>
+          <t>12936800.1698674</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>12.768</t>
+          <t>12767799.736805</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6.476</t>
+          <t>6475725.60334481</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.448</t>
+          <t>6448231.78414933</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.585</t>
+          <t>6585080.46125861</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6.664</t>
+          <t>6664316.05068995</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6.722</t>
+          <t>6722137.61114634</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6.855</t>
+          <t>6855456.93044083</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6729616.88271473</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6.774</t>
+          <t>6774234.12305928</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6.923</t>
+          <t>6922754.85156308</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>7.165</t>
+          <t>7165193.00945672</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>7.366</t>
+          <t>7365679.92931801</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7.553</t>
+          <t>7553390.75098092</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7.745</t>
+          <t>7744755.02693112</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7929677.04096322</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7.907</t>
+          <t>7907097.403946</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>123.518</t>
+          <t>123517774.061721</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>125.56</t>
+          <t>125559547.667366</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>128.056</t>
+          <t>128056194.03076</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>131.603</t>
+          <t>131602779.036991</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>134.466</t>
+          <t>134466483.527903</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>137.538</t>
+          <t>137538255.716162</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>136.742</t>
+          <t>136742105.02754</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>135.486</t>
+          <t>135486090.229891</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>134.951</t>
+          <t>134950540.641539</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>136.496</t>
+          <t>136495929.485433</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>139.146</t>
+          <t>139145642.771284</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>141.466</t>
+          <t>141466015.427866</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>142.838</t>
+          <t>142837532.391284</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>142.317</t>
+          <t>142317140.915456</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>136.175</t>
+          <t>136175097.889172</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>370.557</t>
+          <t>370556518.425133</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>379.509</t>
+          <t>379509221.724772</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>390.19</t>
+          <t>390190196.806831</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>395.691</t>
+          <t>395691036.171245</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>400.131</t>
+          <t>400130624.103076</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>413.204</t>
+          <t>413204257.946556</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>426.421</t>
+          <t>426421156.075177</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>433.848</t>
+          <t>433847564.736811</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>450.765</t>
+          <t>450765196.188898</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>467.784</t>
+          <t>467784408.353138</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>483.061</t>
+          <t>483061497.143057</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>500.543</t>
+          <t>500543459.622823</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>514.72</t>
+          <t>514719589.10591</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>530.955</t>
+          <t>530954814.689202</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>540637734.903813</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1340.302</t>
+          <t>1340302130.8872</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1366.883</t>
+          <t>1366883339.16507</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1397.427</t>
+          <t>1397427297.99206</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1415.446</t>
+          <t>1415445994.83251</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1441.207</t>
+          <t>1441207283.56612</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1481.326</t>
+          <t>1481326410.23864</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1514.24</t>
+          <t>1514240307.893</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1528.087</t>
+          <t>1528087049.69162</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1560.787</t>
+          <t>1560786843.92461</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1599.028</t>
+          <t>1599028460.13363</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1636.236</t>
+          <t>1636235991.91798</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1673.185</t>
+          <t>1673184987.3684</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1700.913</t>
+          <t>1700913042.44847</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1735.034</t>
+          <t>1735034078.36997</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1740.403</t>
+          <t>1740403487.76738</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4462,12 +4467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
